--- a/tests/agent_contract/data/S6_single_filter.xlsx
+++ b/tests/agent_contract/data/S6_single_filter.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,38 +413,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>支付状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>O5000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>产品A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>支付状态</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O5000</t>
+          <t>O5001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -457,7 +470,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3604</v>
+        <v>2800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -468,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O5001</t>
+          <t>O5002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -477,7 +490,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3182</v>
+        <v>3897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -488,7 +501,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O5002</t>
+          <t>O5003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,7 +510,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3196</v>
+        <v>5577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -508,7 +521,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O5003</t>
+          <t>O5004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,7 +530,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4435</v>
+        <v>3282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -528,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O5004</t>
+          <t>O5005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -537,7 +550,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5608</v>
+        <v>2435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -548,7 +561,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O5005</t>
+          <t>O5006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,7 +570,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5383</v>
+        <v>5769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -568,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O5006</t>
+          <t>O5007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -577,7 +590,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2227</v>
+        <v>1103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -588,7 +601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O5007</t>
+          <t>O5008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -597,7 +610,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2678</v>
+        <v>4541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -608,7 +621,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O5008</t>
+          <t>O5009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -617,7 +630,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3575</v>
+        <v>5142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -628,7 +641,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O5009</t>
+          <t>O5010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -637,7 +650,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2547</v>
+        <v>1153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -648,7 +661,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O5010</t>
+          <t>O5011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -657,7 +670,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1458</v>
+        <v>26167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -668,7 +681,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O5011</t>
+          <t>O5012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -677,18 +690,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4793</v>
+        <v>1138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O5012</t>
+          <t>O5013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -697,18 +710,18 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3052</v>
+        <v>1965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O5013</t>
+          <t>O5014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -717,18 +730,18 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19262</v>
+        <v>3085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O5014</t>
+          <t>O5015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -737,7 +750,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5899</v>
+        <v>4327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -748,7 +761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O5015</t>
+          <t>O5016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -757,7 +770,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4158</v>
+        <v>3405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -768,7 +781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O5016</t>
+          <t>O5017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -777,7 +790,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2746</v>
+        <v>2918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -788,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O5017</t>
+          <t>O5018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -797,7 +810,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2041</v>
+        <v>1765</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -808,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O5018</t>
+          <t>O5019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -817,7 +830,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5130</v>
+        <v>5174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -828,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O5019</t>
+          <t>O5020</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -837,7 +850,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3708</v>
+        <v>4800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -848,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O5020</t>
+          <t>O5021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -857,7 +870,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5534</v>
+        <v>2847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -868,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O5021</t>
+          <t>O5022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -877,7 +890,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1165</v>
+        <v>2628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -888,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O5022</t>
+          <t>O5023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -897,7 +910,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5633</v>
+        <v>1120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -908,7 +921,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>O5023</t>
+          <t>O5024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -917,7 +930,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4980</v>
+        <v>5857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -928,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O5024</t>
+          <t>O5025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -937,7 +950,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3328</v>
+        <v>1803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -948,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>O5025</t>
+          <t>O5026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -957,7 +970,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4271</v>
+        <v>5983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -968,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>O5026</t>
+          <t>O5027</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -977,7 +990,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2519</v>
+        <v>5698</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -988,7 +1001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>O5027</t>
+          <t>O5028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -997,7 +1010,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4464</v>
+        <v>4191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1008,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>O5028</t>
+          <t>O5029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1017,7 +1030,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4428</v>
+        <v>1752</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1028,7 +1041,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>O5029</t>
+          <t>O5030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1037,7 +1050,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4799</v>
+        <v>3436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1048,7 +1061,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>O5030</t>
+          <t>O5031</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1057,18 +1070,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2148</v>
+        <v>4946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O5031</t>
+          <t>O5032</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1077,7 +1090,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4745</v>
+        <v>4684</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1088,7 +1101,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O5032</t>
+          <t>O5033</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1097,7 +1110,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5521</v>
+        <v>1830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1108,127 +1121,127 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O5033</t>
+          <t>O5034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4623</v>
+        <v>5597</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O5034</t>
+          <t>O5035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2119</v>
+        <v>5056</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>O5035</t>
+          <t>O5036</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5192</v>
+        <v>4974</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>O5036</t>
+          <t>O5037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3059</v>
+        <v>1917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>O5037</t>
+          <t>O5038</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5377</v>
+        <v>1640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>O5038</t>
+          <t>O5039</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>产品B</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2921</v>
+        <v>2854</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>O5039</t>
+          <t>O5040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1237,7 +1250,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2635</v>
+        <v>1557</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1248,7 +1261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>O5040</t>
+          <t>O5041</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1257,7 +1270,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2405</v>
+        <v>2742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1268,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>O5041</t>
+          <t>O5042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1277,7 +1290,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1148</v>
+        <v>5402</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1288,7 +1301,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>O5042</t>
+          <t>O5043</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1297,7 +1310,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5963</v>
+        <v>2894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1308,7 +1321,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>O5043</t>
+          <t>O5044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1317,7 +1330,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5971</v>
+        <v>1805</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1328,7 +1341,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>O5044</t>
+          <t>O5045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1337,7 +1350,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6587</v>
+        <v>4695</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1348,7 +1361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>O5045</t>
+          <t>O5046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1361,14 +1374,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>O5046</t>
+          <t>O5047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1377,18 +1390,18 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4111</v>
+        <v>2605</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>O5047</t>
+          <t>O5048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1397,18 +1410,18 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1912</v>
+        <v>23415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>O5048</t>
+          <t>O5049</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1417,7 +1430,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3959</v>
+        <v>4394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1428,7 +1441,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>O5049</t>
+          <t>O5050</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1437,7 +1450,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1696</v>
+        <v>1939</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1448,7 +1461,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>O5050</t>
+          <t>O5051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1457,7 +1470,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2692</v>
+        <v>4947</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1468,7 +1481,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>O5051</t>
+          <t>O5052</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1477,7 +1490,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4051</v>
+        <v>2485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1488,7 +1501,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>O5052</t>
+          <t>O5053</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1497,7 +1510,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4451</v>
+        <v>4326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1508,7 +1521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>O5053</t>
+          <t>O5054</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1517,7 +1530,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2166</v>
+        <v>3781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1528,7 +1541,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>O5054</t>
+          <t>O5055</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1537,7 +1550,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3507</v>
+        <v>4864</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1548,7 +1561,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O5055</t>
+          <t>O5056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1557,7 +1570,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3894</v>
+        <v>5913</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1568,7 +1581,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O5056</t>
+          <t>O5057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1577,7 +1590,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2031</v>
+        <v>2237</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1588,7 +1601,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O5057</t>
+          <t>O5058</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1597,7 +1610,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4925</v>
+        <v>5391</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1608,7 +1621,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>O5058</t>
+          <t>O5059</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1617,7 +1630,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3992</v>
+        <v>3448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1628,7 +1641,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>O5059</t>
+          <t>O5060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1637,7 +1650,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5993</v>
+        <v>1246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1648,7 +1661,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>O5060</t>
+          <t>O5061</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1657,7 +1670,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1666</v>
+        <v>2036</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1668,7 +1681,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>O5061</t>
+          <t>O5062</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1677,7 +1690,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1174</v>
+        <v>1362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1688,7 +1701,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O5062</t>
+          <t>O5063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1697,7 +1710,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1071</v>
+        <v>1257</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1708,7 +1721,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>O5063</t>
+          <t>O5064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1717,7 +1730,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1010</v>
+        <v>1026</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1728,7 +1741,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>O5064</t>
+          <t>O5065</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1737,7 +1750,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1002</v>
+        <v>1113</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1748,7 +1761,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>O5065</t>
+          <t>O5066</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1757,18 +1770,18 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1118</v>
+        <v>2495</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>O5066</t>
+          <t>O5067</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1777,7 +1790,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5569</v>
+        <v>3188</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1788,7 +1801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>O5067</t>
+          <t>O5068</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1797,7 +1810,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2444</v>
+        <v>1657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1808,67 +1821,67 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>O5068</t>
+          <t>O5069</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2738</v>
+        <v>2452</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>O5069</t>
+          <t>O5070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2587</v>
+        <v>1565</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>O5070</t>
+          <t>O5071</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>产品D</t>
+          <t>产品E</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2617</v>
+        <v>3337</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>O5071</t>
+          <t>O5072</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1877,7 +1890,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3759</v>
+        <v>2109</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1888,7 +1901,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>O5072</t>
+          <t>O5073</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1897,7 +1910,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2900</v>
+        <v>4486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1908,7 +1921,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>O5073</t>
+          <t>O5074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1917,7 +1930,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5718</v>
+        <v>4577</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -1928,7 +1941,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>O5074</t>
+          <t>O5075</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1937,7 +1950,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2509</v>
+        <v>1475</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1948,7 +1961,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>O5075</t>
+          <t>O5076</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1957,7 +1970,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1839</v>
+        <v>1496</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1968,7 +1981,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>O5076</t>
+          <t>O5077</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1977,7 +1990,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2144</v>
+        <v>1499</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1988,7 +2001,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>O5077</t>
+          <t>O5078</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1997,7 +2010,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1217</v>
+        <v>1000</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2008,7 +2021,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>O5078</t>
+          <t>O5079</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2017,7 +2030,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2692</v>
+        <v>1000</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2028,7 +2041,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>O5079</t>
+          <t>O5080</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2037,7 +2050,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1121</v>
+        <v>1001</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2048,7 +2061,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>O5080</t>
+          <t>O5081</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2057,7 +2070,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1042</v>
+        <v>1000</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2068,7 +2081,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>O5081</t>
+          <t>O5082</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2077,7 +2090,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1030</v>
+        <v>1003</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2088,7 +2101,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>O5082</t>
+          <t>O5083</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2097,18 +2110,18 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1010</v>
+        <v>2362</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>O5083</t>
+          <t>O5084</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2117,18 +2130,18 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1019</v>
+        <v>3926</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>O5084</t>
+          <t>O5085</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2137,7 +2150,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3448</v>
+        <v>1590</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2148,7 +2161,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>O5085</t>
+          <t>O5086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2157,7 +2170,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1898</v>
+        <v>1061</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2168,7 +2181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>O5086</t>
+          <t>O5087</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2177,7 +2190,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2080</v>
+        <v>2538</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2188,7 +2201,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>O5087</t>
+          <t>O5088</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2197,7 +2210,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4360</v>
+        <v>4754</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2208,7 +2221,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>O5088</t>
+          <t>O5089</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2217,7 +2230,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2123</v>
+        <v>5446</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2228,67 +2241,67 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>O5089</t>
+          <t>O5090</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2258</v>
+        <v>4651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>O5090</t>
+          <t>O5091</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2820</v>
+        <v>2833</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>O5091</t>
+          <t>O5092</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>产品E</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1406</v>
+        <v>1106</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>O5092</t>
+          <t>O5093</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2297,7 +2310,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3040</v>
+        <v>2247</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2308,7 +2321,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>O5093</t>
+          <t>O5094</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2317,7 +2330,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4516</v>
+        <v>1135</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2328,7 +2341,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>O5094</t>
+          <t>O5095</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2337,7 +2350,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3816</v>
+        <v>1023</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2348,7 +2361,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>O5095</t>
+          <t>O5096</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2357,7 +2370,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4692</v>
+        <v>1003</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2368,7 +2381,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>O5096</t>
+          <t>O5097</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2377,7 +2390,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1121</v>
+        <v>1000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2388,7 +2401,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>O5097</t>
+          <t>O5098</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2397,7 +2410,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1766</v>
+        <v>1002</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2408,7 +2421,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>O5098</t>
+          <t>O5099</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2417,7 +2430,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2428,7 +2441,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>O5099</t>
+          <t>O5100</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2437,7 +2450,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1032</v>
+        <v>1000</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -2448,7 +2461,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>O5100</t>
+          <t>O5101</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2457,7 +2470,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -2468,7 +2481,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>O5101</t>
+          <t>O5102</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2477,18 +2490,18 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4974</v>
+        <v>1000</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>O5102</t>
+          <t>O5103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2497,18 +2510,18 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4624</v>
+        <v>1000</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>O5103</t>
+          <t>O5104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2517,18 +2530,18 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4787</v>
+        <v>1000</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>O5104</t>
+          <t>O5105</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2537,7 +2550,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1387</v>
+        <v>3435</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -2548,7 +2561,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>O5105</t>
+          <t>O5106</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2557,7 +2570,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1735</v>
+        <v>5267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -2568,7 +2581,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>O5106</t>
+          <t>O5107</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2577,7 +2590,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1336</v>
+        <v>5577</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2588,87 +2601,87 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>O5107</t>
+          <t>O5108</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>产品G</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5011</v>
+        <v>3941</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>O5108</t>
+          <t>O5109</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>产品G</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1638</v>
+        <v>3054</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>O5109</t>
+          <t>O5110</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>产品G</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2165</v>
+        <v>5217</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>O5110</t>
+          <t>O5111</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>产品G</t>
+          <t>产品F</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1044</v>
+        <v>2142</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>O5111</t>
+          <t>O5112</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2677,7 +2690,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1008</v>
+        <v>2307</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -2688,7 +2701,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>O5112</t>
+          <t>O5113</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2697,7 +2710,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1002</v>
+        <v>3568</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -2708,7 +2721,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>O5113</t>
+          <t>O5114</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2717,7 +2730,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1056</v>
+        <v>3146</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -2728,7 +2741,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>O5114</t>
+          <t>O5115</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2737,7 +2750,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1012</v>
+        <v>1275</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -2748,7 +2761,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>O5115</t>
+          <t>O5116</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2757,7 +2770,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1056</v>
+        <v>2503</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -2768,7 +2781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>O5116</t>
+          <t>O5117</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2777,7 +2790,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1002</v>
+        <v>1058</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2788,7 +2801,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>O5117</t>
+          <t>O5118</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2797,7 +2810,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1003</v>
+        <v>1068</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2808,7 +2821,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>O5118</t>
+          <t>O5119</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2817,7 +2830,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1003</v>
+        <v>1025</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2828,7 +2841,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>O5119</t>
+          <t>O5120</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2837,18 +2850,18 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>5005</v>
+        <v>1015</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>O5120</t>
+          <t>O5121</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2857,18 +2870,18 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3886</v>
+        <v>1035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>O5121</t>
+          <t>O5122</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2877,7 +2890,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2445</v>
+        <v>5047</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -2888,147 +2901,147 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>O5122</t>
+          <t>O5123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1000</v>
+        <v>4828</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>O5123</t>
+          <t>O5124</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1000</v>
+        <v>4860</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>O5124</t>
+          <t>O5125</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1000</v>
+        <v>5073</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>O5125</t>
+          <t>O5126</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1000</v>
+        <v>5937</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>O5126</t>
+          <t>O5127</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1000</v>
+        <v>5033</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>O5127</t>
+          <t>O5128</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1000</v>
+        <v>2202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>O5128</t>
+          <t>O5129</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>产品H</t>
+          <t>产品G</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1000</v>
+        <v>2562</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未支付</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>O5129</t>
+          <t>O5130</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3048,7 +3061,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>O5130</t>
+          <t>O5131</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3068,7 +3081,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>O5131</t>
+          <t>O5132</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3088,7 +3101,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>O5132</t>
+          <t>O5133</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3097,7 +3110,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3108,7 +3121,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>O5133</t>
+          <t>O5134</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3117,18 +3130,18 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1842</v>
+        <v>1000</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>O5134</t>
+          <t>O5135</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3137,18 +3150,18 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2479</v>
+        <v>1000</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>未支付</t>
+          <t>已支付</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>O5135</t>
+          <t>O5136</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3157,9 +3170,309 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3722</v>
+        <v>1000</v>
       </c>
       <c r="D138" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>O5137</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>O5138</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>O5139</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>O5140</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>O5141</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>O5142</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>O5143</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>O5144</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>3878</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>O5145</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>O5146</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>4950</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>O5147</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1808</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>O5148</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2654</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>O5149</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>4193</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>O5150</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2675</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>未支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>O5151</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>产品H</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>5751</v>
+      </c>
+      <c r="D153" t="inlineStr">
         <is>
           <t>未支付</t>
         </is>
